--- a/Google drive web app.xlsx
+++ b/Google drive web app.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1D1427-36F8-42AE-AFB8-54034EFC346D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4343988E-F02A-4502-B524-FE69A05AD836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="95">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -344,10 +344,19 @@
     <t>Verify the new menu is displayed with available option.</t>
   </si>
   <si>
-    <t>Verify an appropriate error message is displayed.</t>
+    <t>Verify user is successfully logged in and the drive page is displayed.</t>
   </si>
   <si>
-    <t>Verify user is successfully logged in and the drive page is displayed.</t>
+    <t>Installing Google Drive</t>
+  </si>
+  <si>
+    <t>Accessible Internet</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Suhani Dehankar</t>
+  </si>
+  <si>
+    <t>Verify an error message is displayed.</t>
   </si>
 </sst>
 </file>
@@ -821,63 +830,63 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -894,6 +903,113 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>102976</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>361617</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>508429</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1164882</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A855DC9-952A-2565-7793-4A945DB33BFD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect t="38898" b="35917"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2310459" y="3463678"/>
+          <a:ext cx="1435183" cy="803265"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>180204</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>482687</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>497166</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1280727</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{514BDE5E-2406-679D-3CD8-B4B4D5904D7E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect t="36967" b="33649"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2387687" y="5792231"/>
+          <a:ext cx="1346692" cy="798040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1095,21 +1211,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y994"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" customWidth="1"/>
-    <col min="6" max="25" width="9.109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" customWidth="1"/>
+    <col min="6" max="25" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="16.5" customHeight="1">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
+      <c r="B1" s="29"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1117,13 +1233,13 @@
         <v>2</v>
       </c>
       <c r="E1" s="3"/>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="32"/>
       <c r="K1" s="23"/>
       <c r="L1" s="23"/>
       <c r="M1" s="23"/>
@@ -1141,10 +1257,10 @@
       <c r="Y1" s="23"/>
     </row>
     <row r="2" spans="1:25" ht="16.5" customHeight="1">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="33"/>
+      <c r="B2" s="34"/>
       <c r="C2" s="11" t="s">
         <v>5</v>
       </c>
@@ -1152,14 +1268,14 @@
         <v>6</v>
       </c>
       <c r="E2" s="6"/>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="47" t="s">
+      <c r="G2" s="34"/>
+      <c r="H2" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="33"/>
+      <c r="I2" s="34"/>
       <c r="J2" s="25" t="s">
         <v>9</v>
       </c>
@@ -1180,10 +1296,10 @@
       <c r="Y2" s="23"/>
     </row>
     <row r="3" spans="1:25" ht="25.5" customHeight="1">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="33"/>
+      <c r="B3" s="34"/>
       <c r="C3" s="11" t="s">
         <v>11</v>
       </c>
@@ -1191,14 +1307,14 @@
         <v>12</v>
       </c>
       <c r="E3" s="6"/>
-      <c r="F3" s="48">
+      <c r="F3" s="50">
         <v>46220</v>
       </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="47" t="s">
+      <c r="G3" s="34"/>
+      <c r="H3" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="33"/>
+      <c r="I3" s="34"/>
       <c r="J3" s="26" t="s">
         <v>14</v>
       </c>
@@ -1249,21 +1365,21 @@
       <c r="A5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="33"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="34"/>
       <c r="E5" s="14"/>
       <c r="F5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="47" t="s">
+      <c r="G5" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="35"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="40"/>
       <c r="K5" s="23"/>
       <c r="L5" s="23"/>
       <c r="M5" s="23"/>
@@ -1284,21 +1400,21 @@
       <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="33"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="11"/>
       <c r="F6" s="17">
         <v>1</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="35"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="40"/>
       <c r="K6" s="23"/>
       <c r="L6" s="23"/>
       <c r="M6" s="23"/>
@@ -1319,21 +1435,21 @@
       <c r="A7" s="16">
         <v>2</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="33"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="34"/>
       <c r="E7" s="11"/>
       <c r="F7" s="17">
         <v>2</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="35"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="40"/>
       <c r="K7" s="23"/>
       <c r="L7" s="23"/>
       <c r="M7" s="23"/>
@@ -1354,17 +1470,17 @@
       <c r="A8" s="16">
         <v>3</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="33"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="11"/>
       <c r="F8" s="17">
         <v>3</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="35"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="40"/>
       <c r="K8" s="23"/>
       <c r="L8" s="23"/>
       <c r="M8" s="23"/>
@@ -1385,17 +1501,17 @@
       <c r="A9" s="18">
         <v>4</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="29"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44"/>
       <c r="E9" s="19"/>
       <c r="F9" s="20">
         <v>4</v>
       </c>
-      <c r="G9" s="28"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="31"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="45"/>
       <c r="K9" s="27"/>
       <c r="L9" s="23"/>
       <c r="M9" s="23"/>
@@ -1443,17 +1559,17 @@
       <c r="A11" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
       <c r="K11" s="23"/>
       <c r="L11" s="23"/>
       <c r="M11" s="23"/>
@@ -1472,17 +1588,17 @@
     </row>
     <row r="12" spans="1:25" ht="13.5" customHeight="1">
       <c r="A12" s="23"/>
-      <c r="B12" s="36" t="s">
+      <c r="B12" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="37"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
       <c r="M12" s="23"/>
@@ -1526,27 +1642,27 @@
       <c r="X13" s="23"/>
       <c r="Y13" s="23"/>
     </row>
-    <row r="14" spans="1:25" ht="13.8">
+    <row r="14" spans="1:25" ht="12.75">
       <c r="A14" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="38" t="s">
+      <c r="C14" s="29"/>
+      <c r="D14" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="39"/>
-      <c r="F14" s="38" t="s">
+      <c r="E14" s="29"/>
+      <c r="F14" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="40"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="38" t="s">
+      <c r="G14" s="31"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="J14" s="41"/>
+      <c r="J14" s="32"/>
       <c r="K14" s="23"/>
       <c r="L14" s="23"/>
       <c r="M14" s="23"/>
@@ -1567,23 +1683,23 @@
       <c r="A15" s="16">
         <v>1</v>
       </c>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="33"/>
-      <c r="D15" s="32" t="s">
+      <c r="C15" s="34"/>
+      <c r="D15" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="32" t="s">
+      <c r="E15" s="34"/>
+      <c r="F15" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="34"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="32" t="s">
+      <c r="G15" s="39"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="35"/>
+      <c r="J15" s="40"/>
       <c r="K15" s="23"/>
       <c r="L15" s="23"/>
       <c r="M15" s="23"/>
@@ -1604,23 +1720,23 @@
       <c r="A16" s="16">
         <v>2</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="32" t="s">
+      <c r="C16" s="34"/>
+      <c r="D16" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="33"/>
-      <c r="F16" s="32" t="s">
+      <c r="E16" s="34"/>
+      <c r="F16" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="34"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="32" t="s">
+      <c r="G16" s="39"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="35"/>
+      <c r="J16" s="40"/>
       <c r="K16" s="23"/>
       <c r="L16" s="23"/>
       <c r="M16" s="23"/>
@@ -1637,27 +1753,27 @@
       <c r="X16" s="23"/>
       <c r="Y16" s="23"/>
     </row>
-    <row r="17" spans="1:25" ht="13.8">
+    <row r="17" spans="1:25" ht="12.75">
       <c r="A17" s="16">
         <v>3</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="32" t="s">
+      <c r="C17" s="34"/>
+      <c r="D17" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="33"/>
-      <c r="F17" s="32" t="s">
+      <c r="E17" s="34"/>
+      <c r="F17" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="34"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="32" t="s">
+      <c r="G17" s="39"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J17" s="35"/>
+      <c r="J17" s="40"/>
       <c r="K17" s="23"/>
       <c r="L17" s="23"/>
       <c r="M17" s="23"/>
@@ -1674,27 +1790,27 @@
       <c r="X17" s="23"/>
       <c r="Y17" s="23"/>
     </row>
-    <row r="18" spans="1:25" ht="13.8">
+    <row r="18" spans="1:25" ht="12.75">
       <c r="A18" s="16">
         <v>4</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="32" t="s">
+      <c r="C18" s="34"/>
+      <c r="D18" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="33"/>
-      <c r="F18" s="32" t="s">
+      <c r="E18" s="34"/>
+      <c r="F18" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="34"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="32" t="s">
+      <c r="G18" s="39"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J18" s="35"/>
+      <c r="J18" s="40"/>
       <c r="K18" s="23"/>
       <c r="L18" s="23"/>
       <c r="M18" s="23"/>
@@ -1711,27 +1827,27 @@
       <c r="X18" s="23"/>
       <c r="Y18" s="23"/>
     </row>
-    <row r="19" spans="1:25" ht="13.8">
+    <row r="19" spans="1:25" ht="12.75">
       <c r="A19" s="16">
         <v>5</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="32" t="s">
+      <c r="C19" s="34"/>
+      <c r="D19" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="33"/>
-      <c r="F19" s="32" t="s">
+      <c r="E19" s="34"/>
+      <c r="F19" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="34"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="32" t="s">
+      <c r="G19" s="39"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J19" s="35"/>
+      <c r="J19" s="40"/>
       <c r="K19" s="23"/>
       <c r="L19" s="23"/>
       <c r="M19" s="23"/>
@@ -1748,27 +1864,27 @@
       <c r="X19" s="23"/>
       <c r="Y19" s="23"/>
     </row>
-    <row r="20" spans="1:25" ht="13.8">
+    <row r="20" spans="1:25" ht="12.75">
       <c r="A20" s="16">
         <v>6</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="32" t="s">
+      <c r="C20" s="34"/>
+      <c r="D20" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="33"/>
-      <c r="F20" s="32" t="s">
+      <c r="E20" s="34"/>
+      <c r="F20" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="34"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="32" t="s">
+      <c r="G20" s="39"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="35"/>
+      <c r="J20" s="40"/>
       <c r="K20" s="23"/>
       <c r="L20" s="23"/>
       <c r="M20" s="23"/>
@@ -1785,27 +1901,27 @@
       <c r="X20" s="23"/>
       <c r="Y20" s="23"/>
     </row>
-    <row r="21" spans="1:25" ht="13.8">
+    <row r="21" spans="1:25" ht="12.75">
       <c r="A21" s="16">
         <v>7</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="32" t="s">
+      <c r="C21" s="34"/>
+      <c r="D21" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="33"/>
-      <c r="F21" s="32" t="s">
+      <c r="E21" s="34"/>
+      <c r="F21" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="34"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="32" t="s">
+      <c r="G21" s="39"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J21" s="35"/>
+      <c r="J21" s="40"/>
       <c r="K21" s="23"/>
       <c r="L21" s="23"/>
       <c r="M21" s="23"/>
@@ -1822,27 +1938,27 @@
       <c r="X21" s="23"/>
       <c r="Y21" s="23"/>
     </row>
-    <row r="22" spans="1:25" ht="13.8">
+    <row r="22" spans="1:25" ht="12.75">
       <c r="A22" s="16">
         <v>8</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="32" t="s">
+      <c r="C22" s="34"/>
+      <c r="D22" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="33"/>
-      <c r="F22" s="32" t="s">
+      <c r="E22" s="34"/>
+      <c r="F22" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="34"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="32" t="s">
+      <c r="G22" s="39"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="J22" s="35"/>
+      <c r="J22" s="40"/>
       <c r="K22" s="23"/>
       <c r="L22" s="23"/>
       <c r="M22" s="23"/>
@@ -1863,15 +1979,15 @@
       <c r="A23" s="16">
         <v>9</v>
       </c>
-      <c r="B23" s="32"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="35"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="40"/>
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
       <c r="M23" s="23"/>
@@ -1892,15 +2008,15 @@
       <c r="A24" s="16">
         <v>10</v>
       </c>
-      <c r="B24" s="32"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="35"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="40"/>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
       <c r="M24" s="23"/>
@@ -1921,15 +2037,15 @@
       <c r="A25" s="16">
         <v>11</v>
       </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="35"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="40"/>
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
       <c r="M25" s="23"/>
@@ -1950,15 +2066,15 @@
       <c r="A26" s="16">
         <v>12</v>
       </c>
-      <c r="B26" s="32"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="35"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="40"/>
       <c r="K26" s="23"/>
       <c r="L26" s="23"/>
       <c r="M26" s="23"/>
@@ -1979,15 +2095,15 @@
       <c r="A27" s="16">
         <v>13</v>
       </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="35"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="40"/>
       <c r="K27" s="23"/>
       <c r="L27" s="23"/>
       <c r="M27" s="23"/>
@@ -2008,15 +2124,15 @@
       <c r="A28" s="16">
         <v>14</v>
       </c>
-      <c r="B28" s="32"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="35"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="40"/>
       <c r="K28" s="23"/>
       <c r="L28" s="23"/>
       <c r="M28" s="23"/>
@@ -2037,15 +2153,15 @@
       <c r="A29" s="16">
         <v>15</v>
       </c>
-      <c r="B29" s="32"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="35"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="40"/>
       <c r="K29" s="23"/>
       <c r="L29" s="23"/>
       <c r="M29" s="23"/>
@@ -2066,15 +2182,15 @@
       <c r="A30" s="16">
         <v>16</v>
       </c>
-      <c r="B30" s="32"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="35"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="40"/>
       <c r="K30" s="23"/>
       <c r="L30" s="23"/>
       <c r="M30" s="23"/>
@@ -2095,15 +2211,15 @@
       <c r="A31" s="16">
         <v>17</v>
       </c>
-      <c r="B31" s="32"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="35"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="40"/>
       <c r="K31" s="23"/>
       <c r="L31" s="23"/>
       <c r="M31" s="23"/>
@@ -2124,15 +2240,15 @@
       <c r="A32" s="16">
         <v>18</v>
       </c>
-      <c r="B32" s="32"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="35"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="40"/>
       <c r="K32" s="23"/>
       <c r="L32" s="23"/>
       <c r="M32" s="23"/>
@@ -2153,15 +2269,15 @@
       <c r="A33" s="16">
         <v>19</v>
       </c>
-      <c r="B33" s="32"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="35"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="40"/>
       <c r="K33" s="23"/>
       <c r="L33" s="23"/>
       <c r="M33" s="23"/>
@@ -2182,15 +2298,15 @@
       <c r="A34" s="18">
         <v>20</v>
       </c>
-      <c r="B34" s="28"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="31"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="45"/>
       <c r="K34" s="23"/>
       <c r="L34" s="23"/>
       <c r="M34" s="23"/>
@@ -28129,94 +28245,6 @@
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:J30"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="D34:E34"/>
     <mergeCell ref="F34:H34"/>
@@ -28233,6 +28261,94 @@
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="F33:H33"/>
     <mergeCell ref="I33:J33"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="G5:J5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B15" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -28245,23 +28361,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" customWidth="1"/>
-    <col min="3" max="3" width="16.5546875" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" customWidth="1"/>
-    <col min="7" max="7" width="6.5546875" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="6.77734375" customWidth="1"/>
-    <col min="10" max="10" width="5.109375" customWidth="1"/>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="6.5703125" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" customWidth="1"/>
+    <col min="10" max="10" width="5.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27" customHeight="1">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
+      <c r="B1" s="29"/>
       <c r="C1" s="1" t="s">
         <v>48</v>
       </c>
@@ -28269,19 +28385,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="3"/>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41"/>
-    </row>
-    <row r="2" spans="1:10" ht="27.6">
-      <c r="A2" s="46" t="s">
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="32"/>
+    </row>
+    <row r="2" spans="1:10" ht="25.5">
+      <c r="A2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="33"/>
+      <c r="B2" s="34"/>
       <c r="C2" s="11" t="s">
         <v>49</v>
       </c>
@@ -28289,23 +28405,23 @@
         <v>6</v>
       </c>
       <c r="E2" s="6"/>
-      <c r="F2" s="51" t="s">
-        <v>46</v>
+      <c r="F2" s="41" t="s">
+        <v>93</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="47" t="s">
+      <c r="G2" s="34"/>
+      <c r="H2" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="33"/>
+      <c r="I2" s="34"/>
       <c r="J2" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="39" customHeight="1">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="33"/>
+      <c r="B3" s="34"/>
       <c r="C3" s="4" t="s">
         <v>46</v>
       </c>
@@ -28313,19 +28429,19 @@
         <v>12</v>
       </c>
       <c r="E3" s="6"/>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="47" t="s">
+      <c r="G3" s="34"/>
+      <c r="H3" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="33"/>
+      <c r="I3" s="34"/>
       <c r="J3" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="13.8">
+    <row r="4" spans="1:10">
       <c r="A4" s="9"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -28337,95 +28453,99 @@
       <c r="I4" s="11"/>
       <c r="J4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="13.8">
+    <row r="5" spans="1:10">
       <c r="A5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="33"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="34"/>
       <c r="E5" s="14"/>
       <c r="F5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="47" t="s">
+      <c r="G5" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="35"/>
-    </row>
-    <row r="6" spans="1:10" ht="13.8">
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="40"/>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="33"/>
+      <c r="B6" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="39"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="11"/>
       <c r="F6" s="17">
         <v>1</v>
       </c>
-      <c r="G6" s="51" t="s">
+      <c r="G6" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="35"/>
-    </row>
-    <row r="7" spans="1:10" ht="13.8">
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="40"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="16">
         <v>2</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="33"/>
+      <c r="B7" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="39"/>
+      <c r="D7" s="34"/>
       <c r="E7" s="11"/>
       <c r="F7" s="17">
         <v>2</v>
       </c>
-      <c r="G7" s="51" t="s">
+      <c r="G7" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="35"/>
-    </row>
-    <row r="8" spans="1:10" ht="13.8">
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="40"/>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="16">
         <v>3</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="33"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="11"/>
       <c r="F8" s="17">
         <v>3</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="35"/>
-    </row>
-    <row r="9" spans="1:10" ht="13.8">
+      <c r="G8" s="41"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="40"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="18">
         <v>4</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="29"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44"/>
       <c r="E9" s="19"/>
       <c r="F9" s="20">
         <v>4</v>
       </c>
-      <c r="G9" s="28"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="31"/>
-    </row>
-    <row r="10" spans="1:10" ht="13.8">
+      <c r="G9" s="42"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="45"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="21"/>
       <c r="B10" s="21"/>
       <c r="C10" s="21"/>
@@ -28437,35 +28557,35 @@
       <c r="I10" s="21"/>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10" ht="41.4">
+    <row r="11" spans="1:10" ht="25.5">
       <c r="A11" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="52"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-    </row>
-    <row r="12" spans="1:10" ht="13.8">
+      <c r="B11" s="46"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="23"/>
-      <c r="B12" s="50" t="s">
+      <c r="B12" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="37"/>
-    </row>
-    <row r="13" spans="1:10" ht="14.4" thickBot="1">
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+    </row>
+    <row r="13" spans="1:10" ht="13.5" thickBot="1">
       <c r="A13" s="23"/>
       <c r="B13" s="23"/>
       <c r="C13" s="23"/>
@@ -28474,389 +28594,389 @@
       <c r="I13" s="23"/>
       <c r="J13" s="23"/>
     </row>
-    <row r="14" spans="1:10" ht="13.8">
+    <row r="14" spans="1:10">
       <c r="A14" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="38" t="s">
+      <c r="C14" s="29"/>
+      <c r="D14" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="39"/>
-      <c r="F14" s="38" t="s">
+      <c r="E14" s="29"/>
+      <c r="F14" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="40"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="38" t="s">
+      <c r="G14" s="31"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="J14" s="41"/>
-    </row>
-    <row r="15" spans="1:10" ht="38.4" customHeight="1">
+      <c r="J14" s="32"/>
+    </row>
+    <row r="15" spans="1:10" ht="96.75" customHeight="1">
       <c r="A15" s="16">
         <v>1</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="34"/>
-      <c r="D15" s="32" t="s">
+      <c r="C15" s="39"/>
+      <c r="D15" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="35"/>
-    </row>
-    <row r="16" spans="1:10" ht="44.4" customHeight="1">
+      <c r="E15" s="34"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="40"/>
+    </row>
+    <row r="16" spans="1:10" ht="44.45" customHeight="1">
       <c r="A16" s="16">
         <v>2</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="32" t="s">
-        <v>91</v>
+      <c r="C16" s="34"/>
+      <c r="D16" s="41" t="s">
+        <v>90</v>
       </c>
-      <c r="E16" s="33"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="35"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="40"/>
     </row>
     <row r="17" spans="1:10" ht="33.6" customHeight="1">
       <c r="A17" s="16">
         <v>3</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="32" t="s">
-        <v>90</v>
+      <c r="C17" s="34"/>
+      <c r="D17" s="41" t="s">
+        <v>94</v>
       </c>
-      <c r="E17" s="33"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="35"/>
-    </row>
-    <row r="18" spans="1:10" ht="33.6" customHeight="1">
+      <c r="E17" s="34"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="40"/>
+    </row>
+    <row r="18" spans="1:10" ht="105" customHeight="1">
       <c r="A18" s="16">
         <v>4</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="32" t="s">
+      <c r="C18" s="34"/>
+      <c r="D18" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="E18" s="33"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="35"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="40"/>
     </row>
     <row r="19" spans="1:10" ht="30.6" customHeight="1">
       <c r="A19" s="16">
         <v>5</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="32" t="s">
+      <c r="C19" s="34"/>
+      <c r="D19" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="E19" s="33"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="35"/>
-    </row>
-    <row r="20" spans="1:10" ht="34.799999999999997" customHeight="1">
+      <c r="E19" s="34"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="40"/>
+    </row>
+    <row r="20" spans="1:10" ht="34.9" customHeight="1">
       <c r="A20" s="16">
         <v>6</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="32" t="s">
+      <c r="C20" s="34"/>
+      <c r="D20" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="33"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="35"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="40"/>
     </row>
     <row r="21" spans="1:10" ht="39.6" customHeight="1">
       <c r="A21" s="16">
         <v>7</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="32" t="s">
+      <c r="C21" s="34"/>
+      <c r="D21" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="33"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="35"/>
-    </row>
-    <row r="22" spans="1:10" ht="41.4" customHeight="1">
+      <c r="E21" s="34"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="40"/>
+    </row>
+    <row r="22" spans="1:10" ht="41.45" customHeight="1">
       <c r="A22" s="16">
         <v>8</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="32" t="s">
+      <c r="C22" s="34"/>
+      <c r="D22" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="33"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="35"/>
-    </row>
-    <row r="23" spans="1:10" ht="34.200000000000003" customHeight="1">
+      <c r="E22" s="34"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="40"/>
+    </row>
+    <row r="23" spans="1:10" ht="34.15" customHeight="1">
       <c r="A23" s="16">
         <v>9</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B23" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="33"/>
-      <c r="D23" s="32" t="s">
+      <c r="C23" s="34"/>
+      <c r="D23" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="33"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="35"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="40"/>
     </row>
     <row r="24" spans="1:10" ht="33" customHeight="1">
       <c r="A24" s="16">
         <v>10</v>
       </c>
-      <c r="B24" s="32" t="s">
+      <c r="B24" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="32" t="s">
+      <c r="C24" s="34"/>
+      <c r="D24" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="E24" s="33"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="35"/>
-    </row>
-    <row r="25" spans="1:10" ht="31.2" customHeight="1">
+      <c r="E24" s="34"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="40"/>
+    </row>
+    <row r="25" spans="1:10" ht="31.15" customHeight="1">
       <c r="A25" s="16">
         <v>11</v>
       </c>
-      <c r="B25" s="32" t="s">
+      <c r="B25" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="33"/>
-      <c r="D25" s="32" t="s">
+      <c r="C25" s="34"/>
+      <c r="D25" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="E25" s="33"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="35"/>
-    </row>
-    <row r="26" spans="1:10" ht="28.8" customHeight="1">
+      <c r="E25" s="34"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="40"/>
+    </row>
+    <row r="26" spans="1:10" ht="28.9" customHeight="1">
       <c r="A26" s="16">
         <v>12</v>
       </c>
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="C26" s="33"/>
-      <c r="D26" s="32" t="s">
+      <c r="C26" s="34"/>
+      <c r="D26" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="E26" s="33"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="35"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="40"/>
     </row>
     <row r="27" spans="1:10" ht="27" customHeight="1">
       <c r="A27" s="16">
         <v>13</v>
       </c>
-      <c r="B27" s="32" t="s">
+      <c r="B27" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="33"/>
-      <c r="D27" s="32" t="s">
+      <c r="C27" s="34"/>
+      <c r="D27" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="E27" s="33"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="35"/>
-    </row>
-    <row r="28" spans="1:10" ht="28.2" customHeight="1">
+      <c r="E27" s="34"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="40"/>
+    </row>
+    <row r="28" spans="1:10" ht="28.15" customHeight="1">
       <c r="A28" s="16">
         <v>14</v>
       </c>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="33"/>
-      <c r="D28" s="32" t="s">
+      <c r="C28" s="34"/>
+      <c r="D28" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="E28" s="33"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="35"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="40"/>
     </row>
     <row r="29" spans="1:10" ht="27" customHeight="1">
       <c r="A29" s="16">
         <v>15</v>
       </c>
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="C29" s="33"/>
-      <c r="D29" s="32" t="s">
+      <c r="C29" s="34"/>
+      <c r="D29" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="E29" s="33"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="35"/>
-    </row>
-    <row r="30" spans="1:10" ht="29.4" customHeight="1">
+      <c r="E29" s="34"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="40"/>
+    </row>
+    <row r="30" spans="1:10" ht="29.45" customHeight="1">
       <c r="A30" s="16">
         <v>16</v>
       </c>
-      <c r="B30" s="32" t="s">
+      <c r="B30" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="33"/>
-      <c r="D30" s="32" t="s">
+      <c r="C30" s="34"/>
+      <c r="D30" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="E30" s="33"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="35"/>
-    </row>
-    <row r="31" spans="1:10" ht="34.200000000000003" customHeight="1">
+      <c r="E30" s="34"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="40"/>
+    </row>
+    <row r="31" spans="1:10" ht="34.15" customHeight="1">
       <c r="A31" s="16">
         <v>17</v>
       </c>
-      <c r="B31" s="32" t="s">
+      <c r="B31" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="C31" s="33"/>
-      <c r="D31" s="32" t="s">
+      <c r="C31" s="34"/>
+      <c r="D31" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="E31" s="33"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="35"/>
-    </row>
-    <row r="32" spans="1:10" ht="34.200000000000003" customHeight="1">
+      <c r="E31" s="34"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="40"/>
+    </row>
+    <row r="32" spans="1:10" ht="34.15" customHeight="1">
       <c r="A32" s="16">
         <v>18</v>
       </c>
-      <c r="B32" s="32" t="s">
+      <c r="B32" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="C32" s="33"/>
-      <c r="D32" s="32" t="s">
+      <c r="C32" s="34"/>
+      <c r="D32" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="E32" s="33"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="35"/>
-    </row>
-    <row r="33" spans="1:10" ht="34.799999999999997" customHeight="1">
+      <c r="E32" s="34"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="40"/>
+    </row>
+    <row r="33" spans="1:10" ht="34.9" customHeight="1">
       <c r="A33" s="16">
         <v>19</v>
       </c>
-      <c r="B33" s="32" t="s">
+      <c r="B33" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="32" t="s">
+      <c r="C33" s="34"/>
+      <c r="D33" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="E33" s="33"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="35"/>
-    </row>
-    <row r="34" spans="1:10" ht="33.6" customHeight="1">
+      <c r="E33" s="34"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="40"/>
+    </row>
+    <row r="34" spans="1:10" ht="42" customHeight="1">
       <c r="A34" s="18">
         <v>20</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="C34" s="29"/>
-      <c r="D34" s="28" t="s">
+      <c r="C34" s="44"/>
+      <c r="D34" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="E34" s="29"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="31"/>
-    </row>
-    <row r="35" spans="1:10" ht="13.8">
+      <c r="E34" s="44"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="45"/>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="23"/>
       <c r="B35" s="23"/>
       <c r="C35" s="23"/>
@@ -28868,7 +28988,7 @@
       <c r="I35" s="23"/>
       <c r="J35" s="23"/>
     </row>
-    <row r="36" spans="1:10" ht="13.8">
+    <row r="36" spans="1:10">
       <c r="A36" s="23"/>
       <c r="B36" s="23"/>
       <c r="C36" s="23"/>
@@ -28880,7 +29000,7 @@
       <c r="I36" s="23"/>
       <c r="J36" s="23"/>
     </row>
-    <row r="37" spans="1:10" ht="13.8">
+    <row r="37" spans="1:10">
       <c r="A37" s="23"/>
       <c r="B37" s="23"/>
       <c r="C37" s="23"/>
@@ -28892,7 +29012,7 @@
       <c r="I37" s="23"/>
       <c r="J37" s="23"/>
     </row>
-    <row r="38" spans="1:10" ht="13.8">
+    <row r="38" spans="1:10">
       <c r="A38" s="23"/>
       <c r="B38" s="23"/>
       <c r="C38" s="23"/>
@@ -28904,7 +29024,7 @@
       <c r="I38" s="23"/>
       <c r="J38" s="23"/>
     </row>
-    <row r="39" spans="1:10" ht="13.8">
+    <row r="39" spans="1:10">
       <c r="A39" s="23"/>
       <c r="B39" s="23"/>
       <c r="C39" s="23"/>
@@ -28916,7 +29036,7 @@
       <c r="I39" s="23"/>
       <c r="J39" s="23"/>
     </row>
-    <row r="40" spans="1:10" ht="13.8">
+    <row r="40" spans="1:10">
       <c r="A40" s="23"/>
       <c r="B40" s="23"/>
       <c r="C40" s="23"/>
@@ -28928,7 +29048,7 @@
       <c r="I40" s="23"/>
       <c r="J40" s="23"/>
     </row>
-    <row r="41" spans="1:10" ht="13.8">
+    <row r="41" spans="1:10">
       <c r="A41" s="23"/>
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
@@ -28940,7 +29060,7 @@
       <c r="I41" s="23"/>
       <c r="J41" s="23"/>
     </row>
-    <row r="42" spans="1:10" ht="13.8">
+    <row r="42" spans="1:10">
       <c r="A42" s="23"/>
       <c r="B42" s="23"/>
       <c r="C42" s="23"/>
@@ -28952,7 +29072,7 @@
       <c r="I42" s="23"/>
       <c r="J42" s="23"/>
     </row>
-    <row r="43" spans="1:10" ht="13.8">
+    <row r="43" spans="1:10">
       <c r="A43" s="23"/>
       <c r="B43" s="23"/>
       <c r="C43" s="23"/>
@@ -28966,94 +29086,6 @@
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:J30"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="D34:E34"/>
     <mergeCell ref="F34:H34"/>
@@ -29070,8 +29102,97 @@
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="F33:H33"/>
     <mergeCell ref="I33:J33"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="G5:J5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>